--- a/ESTP/PGE2/S7/MethodeElementsFinis/9-Exam/Notes.xlsx
+++ b/ESTP/PGE2/S7/MethodeElementsFinis/9-Exam/Notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://entestp-my.sharepoint.com/personal/mberger_estp_fr/Documents/Documents/Projets/slides/ESTP/PGE2/S7/MethodeElementsFinis/9-Exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="11_F25DC773A252ABDACC1048D7115F5CA65BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97A5702F-0234-4E98-A571-38775F61CA1D}"/>
+  <xr:revisionPtr revIDLastSave="765" documentId="11_F25DC773A252ABDACC1048D7115F5CA65BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F65866BD-77D1-45B4-9460-094527A00950}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>BITTI</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>OBAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -709,80 +712,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R49"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.54296875" customWidth="1"/>
     <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="17" width="4.26953125" customWidth="1"/>
+    <col min="4" max="18" width="4.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C2" t="s">
+    <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="D2" t="s">
         <v>89</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>90</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>91</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>92</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>93</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>94</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>95</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>96</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>97</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>98</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>99</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>100</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>101</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>102</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>104</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>0.5</v>
       </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -791,13 +791,13 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -809,20 +809,20 @@
         <v>1</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3">
+        <v>2</v>
+      </c>
+      <c r="R3">
         <v>1.5</v>
       </c>
-      <c r="R3">
-        <f>+SUM(C3:Q3)</f>
+      <c r="S3">
+        <f>+SUM(D3:R3)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C4">
-        <v>4</v>
-      </c>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="D4">
         <v>4</v>
       </c>
@@ -866,11 +866,14 @@
         <v>4</v>
       </c>
       <c r="R4">
-        <f>SUMPRODUCT(C$3:Q$3,C4:Q4)/4</f>
+        <v>4</v>
+      </c>
+      <c r="S4">
+        <f>SUMPRODUCT(D$3:R$3,D4:R4)/4</f>
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -878,10 +881,10 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -895,16 +898,16 @@
       <c r="H5">
         <v>4</v>
       </c>
-      <c r="J5">
+      <c r="I5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="3">
-        <v>4</v>
-      </c>
-      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3">
         <v>4</v>
       </c>
       <c r="O5">
@@ -914,14 +917,17 @@
         <v>4</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R5">
-        <f>SUMPRODUCT(C$3:Q$3,C5:Q5)/4</f>
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <f>SUMPRODUCT(D$3:R$3,D5:R5)/4</f>
         <v>14.875</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -929,7 +935,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -938,19 +944,19 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
-      <c r="J6">
-        <v>4</v>
+      <c r="H6">
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -961,12 +967,15 @@
       <c r="O6">
         <v>4</v>
       </c>
-      <c r="R6">
-        <f t="shared" ref="R6:R49" si="0">SUMPRODUCT(C$3:Q$3,C6:Q6)/4</f>
+      <c r="P6">
+        <v>4</v>
+      </c>
+      <c r="S6">
+        <f t="shared" ref="S6:S49" si="0">SUMPRODUCT(D$3:R$3,D6:R6)/4</f>
         <v>11.5</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -974,7 +983,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -985,30 +994,33 @@
       <c r="F7">
         <v>4</v>
       </c>
-      <c r="J7">
-        <v>3</v>
+      <c r="G7">
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="N7">
-        <v>4</v>
-      </c>
       <c r="O7">
         <v>4</v>
       </c>
       <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="R7">
+        <v>4</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="S7">
         <f t="shared" si="0"/>
         <v>11.5</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -1016,34 +1028,34 @@
         <v>12</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
         <v>0</v>
       </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
       <c r="K8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8">
         <v>2</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O8">
         <v>4</v>
@@ -1052,14 +1064,17 @@
         <v>4</v>
       </c>
       <c r="Q8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R8">
+        <v>3</v>
+      </c>
+      <c r="S8">
         <f t="shared" si="0"/>
         <v>11.625</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -1067,7 +1082,7 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -1079,19 +1094,19 @@
         <v>4</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="N9">
-        <v>4</v>
+      <c r="L9">
+        <v>0</v>
       </c>
       <c r="O9">
         <v>4</v>
@@ -1100,14 +1115,17 @@
         <v>4</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
         <f t="shared" si="0"/>
         <v>10.875</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -1115,7 +1133,7 @@
         <v>16</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -1127,32 +1145,35 @@
         <v>4</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>4</v>
-      </c>
-      <c r="N10">
-        <v>4</v>
-      </c>
-      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>4</v>
+      </c>
+      <c r="O10">
+        <v>4</v>
+      </c>
+      <c r="S10">
         <f t="shared" si="0"/>
         <v>11.25</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -1160,7 +1181,7 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -1169,35 +1190,38 @@
         <v>4</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>2</v>
-      </c>
-      <c r="N11">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <v>2</v>
       </c>
       <c r="O11">
         <v>4</v>
       </c>
       <c r="P11">
-        <v>3</v>
-      </c>
-      <c r="R11">
+        <v>4</v>
+      </c>
+      <c r="Q11">
+        <v>3</v>
+      </c>
+      <c r="S11">
         <f t="shared" si="0"/>
         <v>12.25</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -1205,13 +1229,13 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1220,13 +1244,13 @@
         <v>1</v>
       </c>
       <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
         <v>0</v>
       </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
       <c r="J12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>4</v>
@@ -1247,14 +1271,17 @@
         <v>4</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R12">
+        <v>2</v>
+      </c>
+      <c r="S12">
         <f t="shared" si="0"/>
         <v>13.75</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1262,7 +1289,7 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>16.5</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -1271,25 +1298,25 @@
         <v>4</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13">
         <v>3</v>
       </c>
       <c r="H13">
-        <v>2</v>
-      </c>
-      <c r="J13">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
       </c>
       <c r="K13">
         <v>4</v>
       </c>
       <c r="L13">
-        <v>2</v>
-      </c>
-      <c r="N13">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
       </c>
       <c r="O13">
         <v>4</v>
@@ -1301,11 +1328,14 @@
         <v>4</v>
       </c>
       <c r="R13">
+        <v>4</v>
+      </c>
+      <c r="S13">
         <f t="shared" si="0"/>
         <v>16.25</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -1313,25 +1343,25 @@
         <v>22</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="D14">
         <v>4</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -1343,11 +1373,11 @@
         <v>4</v>
       </c>
       <c r="M14">
+        <v>4</v>
+      </c>
+      <c r="N14">
         <v>0</v>
       </c>
-      <c r="N14">
-        <v>4</v>
-      </c>
       <c r="O14">
         <v>4</v>
       </c>
@@ -1355,14 +1385,17 @@
         <v>4</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R14">
+        <v>2</v>
+      </c>
+      <c r="S14">
         <f t="shared" si="0"/>
         <v>15.25</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -1370,7 +1403,7 @@
         <v>24</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -1382,21 +1415,21 @@
         <v>4</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15">
         <v>2</v>
       </c>
-      <c r="J15">
-        <v>4</v>
+      <c r="I15">
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15">
-        <v>4</v>
-      </c>
-      <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="M15">
         <v>4</v>
       </c>
       <c r="O15">
@@ -1405,12 +1438,15 @@
       <c r="P15">
         <v>4</v>
       </c>
-      <c r="R15">
+      <c r="Q15">
+        <v>4</v>
+      </c>
+      <c r="S15">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
@@ -1418,7 +1454,7 @@
         <v>26</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -1435,7 +1471,7 @@
       <c r="H16">
         <v>4</v>
       </c>
-      <c r="J16">
+      <c r="I16">
         <v>4</v>
       </c>
       <c r="K16">
@@ -1460,11 +1496,14 @@
         <v>4</v>
       </c>
       <c r="R16">
+        <v>4</v>
+      </c>
+      <c r="S16">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>27</v>
       </c>
@@ -1472,7 +1511,7 @@
         <v>28</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -1499,10 +1538,10 @@
         <v>4</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N17">
         <v>4</v>
@@ -1514,14 +1553,17 @@
         <v>4</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R17">
+        <v>2</v>
+      </c>
+      <c r="S17">
         <f t="shared" si="0"/>
         <v>18.75</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>29</v>
       </c>
@@ -1529,392 +1571,1706 @@
         <v>30</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>12.5</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <v>4</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>4</v>
+      </c>
+      <c r="M18">
+        <v>4</v>
+      </c>
+      <c r="O18">
+        <v>2</v>
+      </c>
+      <c r="P18">
+        <v>4</v>
+      </c>
+      <c r="Q18">
+        <v>3</v>
       </c>
       <c r="R18">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="C19">
+        <v>16</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>4</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>4</v>
+      </c>
+      <c r="L19">
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <v>4</v>
+      </c>
+      <c r="N19">
+        <v>4</v>
+      </c>
+      <c r="O19">
+        <v>4</v>
+      </c>
+      <c r="P19">
+        <v>4</v>
+      </c>
+      <c r="Q19">
+        <v>4</v>
+      </c>
       <c r="R19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="0"/>
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="C20">
+        <v>17</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="K20">
+        <v>4</v>
+      </c>
+      <c r="L20">
+        <v>4</v>
+      </c>
+      <c r="M20">
+        <v>4</v>
+      </c>
+      <c r="N20">
+        <v>4</v>
+      </c>
+      <c r="O20">
+        <v>4</v>
+      </c>
+      <c r="P20">
+        <v>4</v>
+      </c>
+      <c r="Q20">
+        <v>4</v>
+      </c>
       <c r="R20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>4</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <v>3</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="C22">
+        <v>14.5</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>4</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="O22">
+        <v>4</v>
+      </c>
+      <c r="P22">
+        <v>4</v>
+      </c>
+      <c r="Q22">
+        <v>4</v>
+      </c>
       <c r="R22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="0"/>
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="C23">
+        <v>8.5</v>
+      </c>
+      <c r="D23" s="3">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <v>4</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>3</v>
+      </c>
+      <c r="P23">
+        <v>4</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
       <c r="R23">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S23">
+        <f t="shared" si="0"/>
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="C24">
+        <v>17.5</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24">
+        <v>4</v>
+      </c>
+      <c r="H24">
+        <v>4</v>
+      </c>
+      <c r="I24">
+        <v>4</v>
+      </c>
+      <c r="J24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K24">
+        <v>4</v>
+      </c>
+      <c r="L24">
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <v>4</v>
+      </c>
+      <c r="N24">
+        <v>4</v>
+      </c>
+      <c r="O24">
+        <v>4</v>
+      </c>
+      <c r="P24">
+        <v>4</v>
+      </c>
+      <c r="Q24">
+        <v>4</v>
+      </c>
       <c r="R24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="0"/>
+        <v>17.375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="C25">
+        <v>12</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
+      </c>
+      <c r="H25">
+        <v>4</v>
+      </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>4</v>
+      </c>
+      <c r="P25">
+        <v>4</v>
+      </c>
       <c r="R25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="0"/>
+        <v>11.875</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="C26">
+        <v>15.5</v>
+      </c>
+      <c r="D26" s="3">
+        <v>4</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26">
+        <v>4</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="K26">
+        <v>4</v>
+      </c>
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26">
+        <v>2</v>
+      </c>
+      <c r="O26">
+        <v>4</v>
+      </c>
+      <c r="P26">
+        <v>4</v>
+      </c>
+      <c r="Q26">
+        <v>4</v>
+      </c>
       <c r="R26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="0"/>
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="C27">
+        <v>15.5</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="K27">
+        <v>4</v>
+      </c>
+      <c r="L27">
+        <v>2</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <v>4</v>
+      </c>
+      <c r="P27">
+        <v>4</v>
+      </c>
+      <c r="Q27">
+        <v>4</v>
+      </c>
       <c r="R27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="0"/>
+        <v>15.375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="C28">
+        <v>14</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>2</v>
+      </c>
+      <c r="O28">
+        <v>4</v>
+      </c>
+      <c r="P28">
+        <v>4</v>
+      </c>
+      <c r="Q28">
+        <v>4</v>
+      </c>
       <c r="R28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="0"/>
+        <v>14.125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
       <c r="R29">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C30">
+        <v>16</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>2</v>
+      </c>
+      <c r="K30">
+        <v>3</v>
+      </c>
+      <c r="L30">
+        <v>3</v>
+      </c>
+      <c r="M30">
+        <v>4</v>
+      </c>
+      <c r="N30">
+        <v>4</v>
+      </c>
+      <c r="O30">
+        <v>4</v>
+      </c>
+      <c r="P30">
+        <v>4</v>
+      </c>
+      <c r="Q30">
+        <v>3</v>
+      </c>
       <c r="R30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="0"/>
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="C31">
+        <v>10</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>2</v>
+      </c>
+      <c r="M31">
+        <v>4</v>
+      </c>
+      <c r="O31">
+        <v>4</v>
+      </c>
+      <c r="P31">
+        <v>2</v>
+      </c>
+      <c r="Q31">
+        <v>4</v>
+      </c>
       <c r="R31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="S31">
+        <f t="shared" si="0"/>
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="R32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="C32">
+        <v>8.5</v>
+      </c>
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32">
+        <v>2</v>
+      </c>
+      <c r="M32">
+        <v>2</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
+      </c>
+      <c r="O32">
+        <v>4</v>
+      </c>
+      <c r="P32">
+        <v>2</v>
+      </c>
+      <c r="S32">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="C33">
+        <v>14</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33">
+        <v>4</v>
+      </c>
+      <c r="H33">
+        <v>4</v>
+      </c>
+      <c r="I33">
+        <v>3</v>
+      </c>
+      <c r="J33">
+        <v>2</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <v>4</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>4</v>
+      </c>
+      <c r="P33">
+        <v>4</v>
+      </c>
+      <c r="Q33">
+        <v>2</v>
+      </c>
       <c r="R33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="0"/>
+        <v>14.125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="C34">
+        <v>17.5</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34">
+        <v>4</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+      <c r="H34">
+        <v>4</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="K34">
+        <v>4</v>
+      </c>
+      <c r="L34">
+        <v>4</v>
+      </c>
+      <c r="M34">
+        <v>4</v>
+      </c>
+      <c r="N34">
+        <v>4</v>
+      </c>
+      <c r="O34">
+        <v>4</v>
+      </c>
+      <c r="P34">
+        <v>4</v>
+      </c>
+      <c r="Q34">
+        <v>3</v>
+      </c>
       <c r="R34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="S34">
+        <f t="shared" si="0"/>
+        <v>17.625</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="C35">
+        <v>14</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
+      </c>
+      <c r="H35">
+        <v>4</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>4</v>
+      </c>
+      <c r="O35">
+        <v>4</v>
+      </c>
+      <c r="P35">
+        <v>4</v>
+      </c>
+      <c r="Q35">
+        <v>4</v>
+      </c>
       <c r="R35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="S35">
+        <f t="shared" si="0"/>
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="R36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="C36">
+        <v>10.5</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <v>3</v>
+      </c>
+      <c r="M36">
+        <v>4</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36">
+        <v>4</v>
+      </c>
+      <c r="P36">
+        <v>4</v>
+      </c>
+      <c r="Q36">
+        <v>1</v>
+      </c>
+      <c r="S36">
+        <f t="shared" si="0"/>
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>66</v>
       </c>
+      <c r="C37">
+        <v>15.5</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <v>4</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+      <c r="G37">
+        <v>4</v>
+      </c>
+      <c r="H37">
+        <v>4</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>3</v>
+      </c>
+      <c r="K37">
+        <v>3</v>
+      </c>
+      <c r="L37">
+        <v>2</v>
+      </c>
+      <c r="M37">
+        <v>2</v>
+      </c>
+      <c r="O37">
+        <v>4</v>
+      </c>
+      <c r="P37">
+        <v>4</v>
+      </c>
+      <c r="Q37">
+        <v>4</v>
+      </c>
       <c r="R37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="0"/>
+        <v>15.625</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="R38">
-        <f t="shared" si="0"/>
+      <c r="C38">
+        <v>9.5</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38">
+        <v>4</v>
+      </c>
+      <c r="H38">
+        <v>2</v>
+      </c>
+      <c r="I38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J38">
+        <v>2</v>
+      </c>
+      <c r="K38">
+        <v>2</v>
+      </c>
+      <c r="L38">
+        <v>4</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="0"/>
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="C39">
+        <v>10</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="O39">
+        <v>4</v>
+      </c>
+      <c r="P39">
+        <v>4</v>
+      </c>
+      <c r="Q39">
+        <v>4</v>
+      </c>
       <c r="R39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="0"/>
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="C40">
+        <v>13.5</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+      <c r="H40">
+        <v>2</v>
+      </c>
+      <c r="K40">
+        <v>4</v>
+      </c>
+      <c r="L40">
+        <v>2</v>
+      </c>
+      <c r="M40">
+        <v>4</v>
+      </c>
+      <c r="N40">
+        <v>4</v>
+      </c>
+      <c r="O40">
+        <v>2</v>
+      </c>
+      <c r="P40">
+        <v>2</v>
+      </c>
+      <c r="Q40">
+        <v>3</v>
+      </c>
       <c r="R40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="0"/>
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="C41">
+        <v>16.5</v>
+      </c>
+      <c r="D41" s="3">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41">
+        <v>4</v>
+      </c>
+      <c r="H41">
+        <v>4</v>
+      </c>
+      <c r="I41">
+        <v>4</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41">
+        <v>4</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>3</v>
+      </c>
+      <c r="O41">
+        <v>4</v>
+      </c>
+      <c r="P41">
+        <v>4</v>
+      </c>
+      <c r="Q41">
+        <v>4</v>
+      </c>
       <c r="R41">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="0"/>
+        <v>16.375</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="H42">
+        <v>2</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>3</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="O42">
+        <v>2</v>
+      </c>
+      <c r="P42">
+        <v>4</v>
+      </c>
+      <c r="Q42">
+        <v>2</v>
+      </c>
       <c r="R42">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="0"/>
+        <v>10.125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>76</v>
       </c>
+      <c r="C43">
+        <v>15</v>
+      </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43">
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43">
+        <v>4</v>
+      </c>
+      <c r="H43">
+        <v>4</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43">
+        <v>3</v>
+      </c>
+      <c r="L43">
+        <v>4</v>
+      </c>
+      <c r="M43">
+        <v>2</v>
+      </c>
+      <c r="N43">
+        <v>2</v>
+      </c>
+      <c r="O43">
+        <v>4</v>
+      </c>
+      <c r="P43">
+        <v>4</v>
+      </c>
+      <c r="Q43">
+        <v>1</v>
+      </c>
       <c r="R43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="0"/>
+        <v>14.875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="C44">
+        <v>10</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="F44">
+        <v>4</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>2</v>
+      </c>
+      <c r="O44">
+        <v>4</v>
+      </c>
+      <c r="P44">
+        <v>4</v>
+      </c>
+      <c r="Q44">
+        <v>3</v>
+      </c>
       <c r="R44">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="C45">
+        <v>16</v>
+      </c>
+      <c r="D45">
+        <v>4</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45">
+        <v>4</v>
+      </c>
+      <c r="H45">
+        <v>4</v>
+      </c>
+      <c r="I45">
+        <v>4</v>
+      </c>
+      <c r="J45">
+        <v>2</v>
+      </c>
+      <c r="K45">
+        <v>3</v>
+      </c>
+      <c r="L45">
+        <v>2</v>
+      </c>
+      <c r="M45">
+        <v>3</v>
+      </c>
+      <c r="O45">
+        <v>4</v>
+      </c>
+      <c r="P45">
+        <v>4</v>
+      </c>
+      <c r="Q45">
+        <v>4</v>
+      </c>
       <c r="R45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="0"/>
+        <v>15.625</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="C46">
+        <v>18</v>
+      </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="F46">
+        <v>4</v>
+      </c>
+      <c r="G46">
+        <v>4</v>
+      </c>
+      <c r="H46">
+        <v>4</v>
+      </c>
+      <c r="I46">
+        <v>2</v>
+      </c>
+      <c r="J46">
+        <v>2</v>
+      </c>
+      <c r="K46">
+        <v>4</v>
+      </c>
+      <c r="L46">
+        <v>4</v>
+      </c>
+      <c r="M46">
+        <v>2</v>
+      </c>
+      <c r="N46">
+        <v>2</v>
+      </c>
+      <c r="O46">
+        <v>4</v>
+      </c>
+      <c r="P46">
+        <v>4</v>
+      </c>
+      <c r="Q46">
+        <v>4</v>
+      </c>
       <c r="R46">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="S46">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>84</v>
       </c>
+      <c r="C47">
+        <v>15</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47">
+        <v>3</v>
+      </c>
+      <c r="H47">
+        <v>4</v>
+      </c>
+      <c r="I47">
+        <v>4</v>
+      </c>
+      <c r="J47">
+        <v>3</v>
+      </c>
+      <c r="K47">
+        <v>4</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>4</v>
+      </c>
+      <c r="N47">
+        <v>3</v>
+      </c>
+      <c r="O47">
+        <v>2</v>
+      </c>
+      <c r="P47">
+        <v>4</v>
+      </c>
+      <c r="Q47">
+        <v>3</v>
+      </c>
       <c r="R47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="S47">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>86</v>
       </c>
+      <c r="C48">
+        <v>14.5</v>
+      </c>
+      <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+      <c r="F48">
+        <v>4</v>
+      </c>
+      <c r="G48">
+        <v>4</v>
+      </c>
+      <c r="H48">
+        <v>4</v>
+      </c>
+      <c r="I48">
+        <v>4</v>
+      </c>
+      <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="K48">
+        <v>3</v>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48">
+        <v>3</v>
+      </c>
+      <c r="O48">
+        <v>4</v>
+      </c>
+      <c r="P48">
+        <v>4</v>
+      </c>
+      <c r="Q48">
+        <v>3</v>
+      </c>
       <c r="R48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="S48">
+        <f t="shared" si="0"/>
+        <v>14.625</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R49">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C49">
+        <v>9.5</v>
+      </c>
+      <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49">
+        <v>4</v>
+      </c>
+      <c r="F49">
+        <v>4</v>
+      </c>
+      <c r="G49">
+        <v>4</v>
+      </c>
+      <c r="H49">
+        <v>4</v>
+      </c>
+      <c r="I49">
+        <v>4</v>
+      </c>
+      <c r="K49">
+        <v>3</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="S49">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
